--- a/outs/todo/top_results.xlsx
+++ b/outs/todo/top_results.xlsx
@@ -9,13 +9,13 @@
     <sheet name="Top results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Top results'!$A$1:$M$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Top results'!$A$1:$M$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
   <si>
     <t xml:space="preserve">agency</t>
   </si>
@@ -59,6 +59,27 @@
     <t xml:space="preserve">DHHS</t>
   </si>
   <si>
+    <t xml:space="preserve">HRSA-27-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) Service Area Competition (SAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-HRSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forecasted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $22.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No escalation: required capabilities are in-house or contracted, no cost share, about 0.25 FTE fits your staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/c30fddfd-2094-4cf0-ba21-04b6736fc755</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-PS-27-0009</t>
   </si>
   <si>
@@ -68,10 +89,7 @@
     <t xml:space="preserve">HHS-CDC-NCHHSTP</t>
   </si>
   <si>
-    <t xml:space="preserve">forecasted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 70 days to deadline · ~$7.5M implied award · no cost share → Tier 1: writer can act</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 139 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
     <t xml:space="preserve">No escalation: required capabilities are in-house or contracted, no cost share, about 0.5 FTE fits your staff</t>
@@ -89,37 +107,256 @@
     <t xml:space="preserve">HHS-CDC-NCEZID</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 96 days to deadline · ~$110.0M implied award · no cost share → Tier 1: writer can act</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 96 days to deadline · up to $22.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/38e79010-c2a9-4d5f-bf81-cede591318e4</t>
   </si>
   <si>
+    <t xml:space="preserve">HRSA-27-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) 2027 Service Area Competition (SAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $19.2M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/51fa7e21-beca-497f-a0f1-bf175382f77f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 100 days to deadline · up to $15.3M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/6076b54f-ab56-4ed2-81f5-8b43c030a4c0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan White HIV/AIDS Program Part B States/Territories Supplemental Grant Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 166 days to deadline · up to $9.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/be465a8b-8694-4eef-9801-5160a92c7cdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIDS Drug Assistance Program (ADAP) Emergency Relief Funds (ERF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 33 days to deadline · up to $10.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/1613e128-508f-47e1-9bf2-e2c02e7d79b1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetal, Infant, and Child Death Review Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 112 days to deadline · up to $5.1M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/d9551b09-3a45-4dc1-a343-3f09521de9aa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-IP-27-035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expanded Surveillance for Pediatric Infectious Diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-HHSCDCERA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 92 days to deadline · up to $1.1M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b3577f33-eee0-49fb-aeba-2ea0b02fe59e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year 2027 Regional Nutrition Hubs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 62 days to deadline · up to $1.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/8b2aa3e2-733a-44d8-876e-56df42678c9a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The National Network of STI Prevention Training Centers (NNPTC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 143 days to deadline · up to $1.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/217a3975-7543-445d-9638-8026297a75c4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Maternity and Obstetrics Management Strategies Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 202 days to deadline · up to $1.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/741f2935-18c1-4e3e-8f54-f30dc3a6ee80</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-PS-27-0008</t>
   </si>
   <si>
     <t xml:space="preserve">Controlling and Preventing STIs in US Health Departments (CAP-STIs)</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 31 days to deadline · ~$8.5M implied award · no cost share → Tier 1: writer can act</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 103 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/0ff3ace3-70fb-4ef7-b6ba-b93a899a2707</t>
   </si>
   <si>
-    <t xml:space="preserve">RFA-IP-27-035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expanded Surveillance for Pediatric Infectious Diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-CDC-HHSCDCERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 92 days to deadline · ~$5.7M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b3577f33-eee0-49fb-aeba-2ea0b02fe59e</t>
+    <t xml:space="preserve">HRSA-27-046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Residency Planning and Development Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 169 days to deadline · up to $750K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/6bc69d9c-87b7-4329-962c-16c8e3ad553d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-DD-27-0065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surveillance and Case Control Study of Stillbirth and Birth Defects (SUCCSSBD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCBDDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 182 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/91d0d477-b844-4189-8880-bd7a2876b24e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-DD-27-0028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maternal-Child Surveillance and Partnerships for Action, Results, and Knowledge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 208 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/172926e9-5f18-4993-893d-ac73be5bbb9d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holistic and Evidence-Informed Wellness for STI Prevention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 243 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/e511b41d-655a-4869-bfd3-09fbf0c33987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR-FD-23-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufactured Foods Flexible Funding Model (MF-FFM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-FDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · no deadline stated · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-DP-27-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation Research on Coordinated Combinations of Community-Clinical Linkage Strategies for Diabetes Prevention and Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 173 days to deadline · up to $725K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/54666d94-e0dc-44d3-90e6-6eb913f79ca9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan White HIV/AIDS Program (RWHAP) Integrated HIV/AIDS Planning Resource Allocation Cooperative Agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 110 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-OH-27-050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State Occupational Safety and Health Surveillance Program (U60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $685K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/13af439f-7405-4592-9a1e-18c4f7db7622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Health Value Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 171 days to deadline · up to $650K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/33b8d341-8908-46c1-95c1-a8af9be3ccc8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Health Network Development Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 167 days to deadline · up to $500K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/8bb15754-c013-462d-b305-f2a8dd116e08</t>
   </si>
   <si>
     <t xml:space="preserve">CDC-RFA-PS-27-0239</t>
@@ -128,22 +365,34 @@
     <t xml:space="preserve">Strengthening Services to Prevent the Infectious Disease Consequences of Drug Use</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 236 days to deadline · ~$41.2M implied award · no cost share → Tier 1: writer can act</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 236 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/441d2761-0d9c-42ae-a3da-905ce4ed0ca4</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The National Network of STI Prevention Training Centers (NNPTC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 143 days to deadline · ~$4.0M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/217a3975-7543-445d-9638-8026297a75c4</t>
+    <t xml:space="preserve">HRSA-27-039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radiation Exposure Screening and Education Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 237 days to deadline · up to $500K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/188aac01-0056-4dd0-9bde-54cf6ddf113c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telehealth Nutrition Services Network Grant Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 213 days to deadline · up to $300K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/18c0a9f1-fe39-4c7a-8ffd-1d8c656d666f</t>
   </si>
   <si>
     <t xml:space="preserve">HRSA-27-063</t>
@@ -152,216 +401,12 @@
     <t xml:space="preserve">HIV Care Grant Program - Part B States/Territories Formula and AIDS Drug Assistance Program Formula and AIDS Drug Assistance Program Supplemental Awards</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-HRSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 30 days to deadline · ~$24.8M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No escalation: required capabilities are in-house or contracted, no cost share, about 0.25 FTE fits your staff</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 92 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/1d55627c-531e-4a60-95e0-719b256179bf</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holistic and Evidence-Informed Wellness for STI Prevention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 243 days to deadline · ~$3.0M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/e511b41d-655a-4869-bfd3-09fbf0c33987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetal, Infant, and Child Death Review Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 112 days to deadline · ~$5.1M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/d9551b09-3a45-4dc1-a343-3f09521de9aa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DD-27-0065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surveillance and Case Control Study of Stillbirth and Birth Defects (SUCCSSBD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-CDC-NCBDDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 182 days to deadline · ~$2.8M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/91d0d477-b844-4189-8880-bd7a2876b24e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-DP-27-051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementation Research on Coordinated Combinations of Community-Clinical Linkage Strategies for Diabetes Prevention and Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 173 days to deadline · ~$2.5M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/54666d94-e0dc-44d3-90e6-6eb913f79ca9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DD-27-0028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maternal-Child Surveillance and Partnerships for Action, Results, and Knowledge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 208 days to deadline · ~$2.2M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/172926e9-5f18-4993-893d-ac73be5bbb9d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-OH-27-050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State Occupational Safety and Health Surveillance Program (U60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · ~$1.6M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/13af439f-7405-4592-9a1e-18c4f7db7622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan White HIV/AIDS Program Part B States/Territories Supplemental Grant Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 166 days to deadline · ~$1.6M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/be465a8b-8694-4eef-9801-5160a92c7cdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIDS Drug Assistance Program (ADAP) Emergency Relief Funds (ERF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 33 days to deadline · ~$2.5M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/1613e128-508f-47e1-9bf2-e2c02e7d79b1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR-FD-23-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufactured Foods Flexible Funding Model (MF-FFM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-FDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · no deadline stated · award size not stated · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Maternity and Obstetrics Management Strategies Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 202 days to deadline · ~$1.0M implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/741f2935-18c1-4e3e-8f54-f30dc3a6ee80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Residency Planning and Development Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 169 days to deadline · ~$750K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/6bc69d9c-87b7-4329-962c-16c8e3ad553d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan White HIV/AIDS Program (RWHAP) Integrated HIV/AIDS Planning Resource Allocation Cooperative Agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 110 days to deadline · ~$700K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Health Value Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 171 days to deadline · ~$650K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/33b8d341-8908-46c1-95c1-a8af9be3ccc8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radiation Exposure Screening and Education Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 237 days to deadline · ~$486K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/188aac01-0056-4dd0-9bde-54cf6ddf113c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Health Network Development Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 167 days to deadline · ~$391K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/8bb15754-c013-462d-b305-f2a8dd116e08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telehealth Nutrition Services Network Grant Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 213 days to deadline · ~$300K implied award · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/18c0a9f1-fe39-4c7a-8ffd-1d8c656d666f</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDC-RFA-TP22-2201</t>
   </si>
   <si>
@@ -374,7 +419,7 @@
     <t xml:space="preserve">posted</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply · partner needed for emergency management · 134 days to deadline · ~$4.4M implied award · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply · partner needed for emergency management · 134 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">Needs emergency management, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
@@ -383,21 +428,99 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/42a1b238-2c19-47b4-ae58-f4a775231b78</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-DP-27-0072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promoting Population Health through Increased Capacity in Alcohol Epidemiology &amp; the Prevention of Excessive Alcohol Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCCDPHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 212 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/6d44bb23-2a1f-4e12-8d72-c2b5b46195d4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-2026-ACF-ORR-ZU-0019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Study and Post-Release Services for Unaccompanied Alien Children​​</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-ACF-ORR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 366 days to deadline · up to $100.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-CK-26-035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emerging Infections Network - Research for Preventing, Detecting, and Managing Travel-associated Infectious Diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · up to $6.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires funding and monitoring subrecipients; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/10f4a697-e6a1-454a-bb73-74bc933f364a</t>
+  </si>
+  <si>
     <t xml:space="preserve">RFA-OH-24-001</t>
   </si>
   <si>
     <t xml:space="preserve">National Center for Construction Safety and Health Research and Translation (U54)</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply · partner needed for research and rigorous evaluation · 62 days to deadline · ~$28.8M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner</t>
+    <t xml:space="preserve">state agency can apply · partner needed for research and rigorous evaluation · 62 days to deadline · up to $5.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/b307f2ac-767d-4715-be92-f5326db2cd9d</t>
   </si>
   <si>
+    <t xml:space="preserve">HRSA-27-042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Communities Opioid Response Program - Community Systems Development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 188 days to deadline · up to $500K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires funding and monitoring subrecipients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/02b2d236-f596-4aca-874d-b8e364156ddc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) 2027 State and Regional Primary Care Association (PCA) Cooperative Agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing; partner needed for emergency management · 117 days to deadline · up to $4.9M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Needs emergency management, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-CE-27-0024</t>
   </si>
   <si>
@@ -407,7 +530,7 @@
     <t xml:space="preserve">HHS-CDC-NCIPC</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 199 days to deadline · ~$4.5M implied award · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 199 days to deadline · up to $1.2M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner; Requires funding and monitoring subrecipients; Cooperative agreement with a required evaluation</t>
@@ -416,19 +539,46 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/3c36bc50-73ae-42ad-a727-fae640dad5c9</t>
   </si>
   <si>
-    <t xml:space="preserve">RFA-CK-26-035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emerging Infections Network - Research for Preventing, Detecting, and Managing Travel-associated Infectious Diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · ~$15.0M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires funding and monitoring subrecipients; Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/10f4a697-e6a1-454a-bb73-74bc933f364a</t>
+    <t xml:space="preserve">HRSA-27-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infant-Toddler Court Program–National Resource Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $6.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/910a75ad-0418-4091-a436-703280874498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Communities Opioid Response Program - Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 174 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Home Visiting Research, Improvement, Sustainability and Evaluation Center (HV-RISE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 146 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
   </si>
   <si>
     <t xml:space="preserve">RFA-OH-27-049</t>
@@ -437,22 +587,31 @@
     <t xml:space="preserve">NIOSH Centers of Excellence for Total Worker Health® (U19)</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 149 days to deadline · ~$5.8M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 149 days to deadline · up to $1.4M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/43e32c6d-fbbd-4056-8fd4-f64cdebefd41</t>
   </si>
   <si>
+    <t xml:space="preserve">HRSA-27-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infant-Toddler Court Program–State Awards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/3fe27753-0c94-4aa0-b7fb-09712631f269</t>
+  </si>
+  <si>
     <t xml:space="preserve">RFA-CK-26-036</t>
   </si>
   <si>
     <t xml:space="preserve">US Travelers Health Research, Surveillance, Communication, and Outreach Network</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · ~$5.0M implied award · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · up to $1.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">Cooperative agreement with a required evaluation</t>
@@ -461,166 +620,106 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/1a3231f6-36eb-40d1-afe8-232010fa2fe3</t>
   </si>
   <si>
+    <t xml:space="preserve">HRSA-27-058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health Workforce Research Center (HWRC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 160 days to deadline · up to $900K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/9accc70c-9683-4b78-bb7b-e8fdbcff1b47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-CE-27-0039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core State Injury Prevention Program (Core SIPP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 159 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-DP-27-036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot Testing, Implementation, and Evaluation of the Cervical, Breast and Colorectal Cancer Clinical Decision Support Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 174 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/5686905a-446f-4b0d-8885-e1683d35c3f4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Viral Hepatitis Education, Awareness, and Capacity Building for Communities and Providers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 244 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHS-26-MT-144-000-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year 2026 Flood Mitigation Assistance Swift Current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHS-DHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 488 days to deadline · award not stated on Grants.gov · cost share required (25% stated) → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost share required (25% stated): supervisor must approve match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/4802584e-01a8-4435-9ce9-710fbc85cba0</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-DP-27-0043</t>
   </si>
   <si>
     <t xml:space="preserve">Statewide Perinatal Quality Collaboratives: Improving Perinatal Care and Outcomes</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-CDC-NCCDPHP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 215 days to deadline · ~$2.1M implied award · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 215 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/477f11ad-e8c7-40ea-84f3-f5bec6e50e3b</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-2026-ACF-ORR-ZU-0019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Study and Post-Release Services for Unaccompanied Alien Children​​</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-ACF-ORR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 366 days to deadline · ~$27.8M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-DP-27-036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilot Testing, Implementation, and Evaluation of the Cervical, Breast and Colorectal Cancer Clinical Decision Support Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 174 days to deadline · ~$3.6M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/5686905a-446f-4b0d-8885-e1683d35c3f4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Communities Opioid Response Program - Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 174 days to deadline · ~$5.0M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infant-Toddler Court Program–National Resource Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · ~$6.8M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/910a75ad-0418-4091-a436-703280874498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DP-27-0072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promoting Population Health through Increased Capacity in Alcohol Epidemiology &amp; the Prevention of Excessive Alcohol Use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 212 days to deadline · ~$1.0M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/6d44bb23-2a1f-4e12-8d72-c2b5b46195d4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Home Visiting Research, Improvement, Sustainability and Evaluation Center (HV-RISE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 146 days to deadline · ~$5.0M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Communities Opioid Response Program - Community Systems Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 188 days to deadline · ~$500K implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires funding and monitoring subrecipients</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/02b2d236-f596-4aca-874d-b8e364156ddc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Viral Hepatitis Education, Awareness, and Capacity Building for Communities and Providers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 244 days to deadline · ~$2.8M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infant-Toddler Court Program–State Awards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · ~$700K implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/3fe27753-0c94-4aa0-b7fb-09712631f269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year (FY) 2027 State and Regional Primary Care Association (PCA) Cooperative Agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing; partner needed for emergency management · 117 days to deadline · ~$1.5M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Needs emergency management, which DHHS reaches only through a partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-CE-27-0039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core State Injury Prevention Program (Core SIPP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 159 days to deadline · ~$1.4M implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
+    <t xml:space="preserve">RFA-OH-25-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupational Safety and Health Training Project Grants (T03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 757 days to deadline · up to $550K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/0731381f-f39a-4d8f-9f55-701eddc5273b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-CE-27-0052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preventing Violence Affecting Young Lives (PREVAYL 2.0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 215 days to deadline · up to $450K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f2ea8925-6244-47e8-8de5-ffe0007096e7</t>
   </si>
   <si>
     <t xml:space="preserve">CDC-RFA-PS-27-0061</t>
@@ -629,54 +728,12 @@
     <t xml:space="preserve">Demonstration Projects for Whole-Person Health Models for Women Living with HIV in the South</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 166 days to deadline · ~$2.5M implied award · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 166 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/06024144-a58a-42d8-8813-75357d9bb7fe</t>
   </si>
   <si>
-    <t xml:space="preserve">DHS-26-MT-144-000-99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year 2026 Flood Mitigation Assistance Swift Current</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHS-DHS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 488 days to deadline · award size not stated · cost share required (25% stated) → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost share required (25% stated): supervisor must approve match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/4802584e-01a8-4435-9ce9-710fbc85cba0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-OH-25-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupational Safety and Health Training Project Grants (T03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 757 days to deadline · ~$828K implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/0731381f-f39a-4d8f-9f55-701eddc5273b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health Workforce Research Center (HWRC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 160 days to deadline · ~$450K implied award · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/9accc70c-9683-4b78-bb7b-e8fdbcff1b47</t>
-  </si>
-  <si>
     <t xml:space="preserve">VA-GPD-FORECAST-FY2026-FY2028</t>
   </si>
   <si>
@@ -686,7 +743,7 @@
     <t xml:space="preserve">VA-HPGPDP</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for housing stock or assistance · no deadline stated · award size not stated · no cost share → Tier 2: needs supervisor or division</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for housing stock or assistance · no deadline stated · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">Needs housing stock or assistance, which DHHS reaches only through a partner</t>
@@ -704,10 +761,10 @@
     <t xml:space="preserve">HHS-ACF</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 48 days to deadline · ~$9.0M implied award · cost share required (30% stated) → Tier 3: needs secretary or legislature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost share on a ~$9.0M award likely needs a state appropriation (line set at $1.0M); Requires a formal state designation (e.g. by the Governor); Cost share required (30% stated): supervisor must approve match</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 51 days to deadline · up to $15.0M (Grants.gov ceiling) · cost share required (30% stated) → Tier 3: needs secretary or legislature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost share on a ~$15M award likely needs a state appropriation (line set at $1.0M); Requires a formal state designation (e.g. by the Governor); Cost share required (30% stated): supervisor must approve match</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/8d272419-96d1-4898-9706-0d86a1e63c03</t>
@@ -719,10 +776,10 @@
     <t xml:space="preserve">Maternal, Infant, and Early Childhood Home Visiting Program (MIECHV)</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 169 days to deadline · ~$11.6M implied award · cost share required (percentage not published) → Tier 3: needs secretary or legislature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost share on a ~$12M award likely needs a state appropriation (line set at $1.0M); Needs workforce training and credentialing, which DHHS reaches only through a partner; Cost share required (percentage not published): supervisor must approve match</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 169 days to deadline · up to $48.6M (Grants.gov ceiling) · cost share required (percentage not published) → Tier 3: needs secretary or legislature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost share on a ~$49M award likely needs a state appropriation (line set at $1.0M); Needs workforce training and credentialing, which DHHS reaches only through a partner; Cost share required (percentage not published): supervisor must approve match</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/f68cf378-43e2-49b9-a252-a7009c6b81cf</t>
@@ -737,10 +794,10 @@
     <t xml:space="preserve">HHS-OPHS</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 103 days to deadline · ~$2.9M implied award · cost share required (percentage not published) → Tier 3: needs secretary or legislature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost share on a ~$2.9M award likely needs a state appropriation (line set at $1.0M); Cost share required (percentage not published): supervisor must approve match; Requires funding and monitoring subrecipients</t>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 103 days to deadline · up to $22.0M (Grants.gov ceiling) · cost share required (percentage not published) → Tier 3: needs secretary or legislature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost share on a ~$22M award likely needs a state appropriation (line set at $1.0M); Cost share required (percentage not published): supervisor must approve match; Requires funding and monitoring subrecipients</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/770eae58-b245-4431-a4b8-7b1aca9e917f</t>
@@ -758,7 +815,7 @@
     <t xml:space="preserve">VA-CSHF</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply · partner needed for capital construction · no deadline stated · ~$275.0M ceiling · cost share required (35% stated) → Tier 3: needs secretary or legislature</t>
+    <t xml:space="preserve">state agency can apply · partner needed for capital construction · no deadline stated · up to $275.0M (Grants.gov ceiling) · cost share required (35% stated) → Tier 3: needs secretary or legislature</t>
   </si>
   <si>
     <t xml:space="preserve">Cost share on a ~$275M award likely needs a state appropriation (line set at $1.0M); Capital construction project; Requires a formal state designation (e.g. by the Governor); Needs capital construction, which DMVA reaches only through a partner; Cost share required (35% stated): supervisor must approve match</t>
@@ -767,10 +824,28 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/59462b36-6d05-4832-a628-427f72260f3d</t>
   </si>
   <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · no route to behavioral health service delivery; partner needed for housing stock or assistance · no deadline stated · award size not stated · no cost share → Tier 3: needs secretary or legislature</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · no route to behavioral health service delivery; partner needed for housing stock or assistance · no deadline stated · award not stated on Grants.gov · no cost share → Tier 3: needs secretary or legislature</t>
   </si>
   <si>
     <t xml:space="preserve">Needs behavioral health service delivery, which DMVA has no route to; Needs housing stock or assistance, which DMVA reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA-NCA-VLGP-FY2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veterans Legacy Grants Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA-VLGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · no route to public health surveillance · 191 days to deadline · up to $400K (Grants.gov ceiling) · no cost share → Tier 3: needs secretary or legislature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs public health surveillance, which DMVA has no route to</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/8d1358e4-662b-4359-aa77-e553a65a6511</t>
   </si>
 </sst>
 </file>
@@ -1189,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>14</v>
@@ -1204,10 +1279,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>46365</v>
+        <v>46386</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>7500000</v>
+        <v>22024900</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>18</v>
@@ -1230,7 +1305,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>21</v>
@@ -1245,19 +1320,17 @@
         <v>17</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>46391</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>110000000</v>
-      </c>
+        <v>46434</v>
+      </c>
+      <c r="J3" s="3"/>
       <c r="K3" s="3" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -1271,34 +1344,34 @@
         <v>3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>46326</v>
+        <v>46391</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>8474576.27118644</v>
+        <v>22000000</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -1312,34 +1385,34 @@
         <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>46387</v>
+        <v>46386</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>5714285.71428571</v>
+        <v>19182000</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -1353,13 +1426,13 @@
         <v>5</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>16</v>
@@ -1368,10 +1441,10 @@
         <v>17</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>46531</v>
+        <v>46395</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>41250000</v>
+        <v>15335500</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>37</v>
@@ -1394,7 +1467,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>39</v>
@@ -1409,10 +1482,10 @@
         <v>17</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>46438</v>
+        <v>46461</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>4000000</v>
+        <v>9000000</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>41</v>
@@ -1444,25 +1517,25 @@
         <v>44</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>46328</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>46325</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>24809259.2592593</v>
-      </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1479,10 +1552,10 @@
         <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>16</v>
@@ -1491,19 +1564,19 @@
         <v>17</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>46538</v>
+        <v>46407</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>3000000</v>
+        <v>5149000</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -1517,34 +1590,34 @@
         <v>9</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>46387</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>46407</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>5149000</v>
-      </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -1558,34 +1631,34 @@
         <v>10</v>
       </c>
       <c r="D11" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>46357</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="L11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>46477</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>2750000</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -1599,34 +1672,34 @@
         <v>11</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>46438</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="L12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>46468</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -1640,34 +1713,34 @@
         <v>12</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>46497</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="L13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>46503</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>2217391.30434783</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -1681,34 +1754,32 @@
         <v>13</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>46398</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="L14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>46386</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="15">
@@ -1722,34 +1793,34 @@
         <v>14</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>46464</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>750000</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="L15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>46461</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -1763,34 +1834,32 @@
         <v>15</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>46477</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>46328</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="K16" s="3" t="s">
+      <c r="L16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="17">
@@ -1804,30 +1873,32 @@
         <v>16</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="G17" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="3"/>
+      <c r="I17" s="3" t="n">
+        <v>46503</v>
+      </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
@@ -1841,34 +1912,32 @@
         <v>17</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>46538</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="L18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>46497</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -1882,34 +1951,30 @@
         <v>18</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>46464</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>750000</v>
-      </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="20">
@@ -1923,34 +1988,34 @@
         <v>19</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>46468</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>725000</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>46405</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>700000</v>
-      </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="21">
@@ -1964,34 +2029,34 @@
         <v>20</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>46405</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>700000</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>46466</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>650000</v>
-      </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="22">
@@ -2005,34 +2070,34 @@
         <v>21</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>46386</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>685000</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>46532</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>486125</v>
-      </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="23">
@@ -2046,34 +2111,34 @@
         <v>22</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>46466</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>650000</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>46462</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>391304.347826087</v>
-      </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="24">
@@ -2087,34 +2152,34 @@
         <v>23</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>46462</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>46508</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>300000</v>
-      </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="25">
@@ -2122,40 +2187,38 @@
         <v>13</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>46531</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="L25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>46429</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>4424778.76106195</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="26">
@@ -2163,40 +2226,40 @@
         <v>13</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>46357</v>
+        <v>46532</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>28750000</v>
+        <v>500000</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27">
@@ -2204,40 +2267,40 @@
         <v>13</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>129</v>
+        <v>16</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>46494</v>
+        <v>46508</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>4519230.76923077</v>
+        <v>300000</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28">
@@ -2245,40 +2308,38 @@
         <v>13</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>15000000</v>
-      </c>
+        <v>46387</v>
+      </c>
+      <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29">
@@ -2289,37 +2350,37 @@
         <v>2</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>46444</v>
+        <v>46429</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5850000</v>
+        <v>5000000</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30">
@@ -2330,37 +2391,35 @@
         <v>2</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>46331</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>5000000</v>
-      </c>
+        <v>46507</v>
+      </c>
+      <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
@@ -2371,37 +2430,37 @@
         <v>2</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>61</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>46661</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="M31" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>46510</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>2141025.64102564</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="32">
@@ -2412,37 +2471,37 @@
         <v>2</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>60</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>46331</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="M32" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>46661</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>27750000</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="33">
@@ -2453,37 +2512,37 @@
         <v>2</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>46469</v>
+        <v>46357</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>3625000</v>
+        <v>5750000</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34">
@@ -2494,37 +2553,37 @@
         <v>2</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>46469</v>
+        <v>46483</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>5000000</v>
+        <v>500000</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35">
@@ -2535,37 +2594,37 @@
         <v>2</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>58</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>46412</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="M35" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>46498</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>6750000</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="36">
@@ -2576,37 +2635,37 @@
         <v>2</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>58</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>46494</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="M36" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>46507</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>1002916.66666667</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="37">
@@ -2617,37 +2676,37 @@
         <v>2</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>46498</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>46441</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="K37" s="3" t="s">
+      <c r="M37" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="38">
@@ -2658,37 +2717,37 @@
         <v>2</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>46469</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>46483</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>500000</v>
-      </c>
-      <c r="K38" s="3" t="s">
+      <c r="L38" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="L38" s="3" t="s">
+      <c r="M38" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="39">
@@ -2699,16 +2758,16 @@
         <v>2</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>56</v>
       </c>
       <c r="E39" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>16</v>
@@ -2717,19 +2776,19 @@
         <v>17</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>46539</v>
+        <v>46441</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>2750000</v>
+        <v>5000000</v>
       </c>
       <c r="K39" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="M39" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="40">
@@ -2740,37 +2799,37 @@
         <v>2</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>46444</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>46498</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>700000</v>
-      </c>
-      <c r="K40" s="3" t="s">
+      <c r="L40" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="M40" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="41">
@@ -2781,37 +2840,37 @@
         <v>2</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E41" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>46498</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>700000</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>46412</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>1461538.46153846</v>
-      </c>
-      <c r="K41" s="3" t="s">
+      <c r="L41" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M41" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="42">
@@ -2822,37 +2881,37 @@
         <v>2</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E42" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>46331</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="L42" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>46454</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>1423076.92307692</v>
-      </c>
-      <c r="K42" s="3" t="s">
+      <c r="M42" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="43">
@@ -2863,16 +2922,16 @@
         <v>2</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>50</v>
       </c>
       <c r="E43" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>16</v>
@@ -2881,19 +2940,19 @@
         <v>17</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>46461</v>
+        <v>46455</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>2500000</v>
+        <v>900000</v>
       </c>
       <c r="K43" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="44">
@@ -2904,35 +2963,35 @@
         <v>2</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E44" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="G44" s="3" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>46783</v>
+        <v>46454</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="45">
@@ -2943,37 +3002,35 @@
         <v>2</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E45" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>46469</v>
+      </c>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="M45" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>47052</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>827586.206896552</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="46">
@@ -2984,37 +3041,35 @@
         <v>2</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E46" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>46539</v>
+      </c>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M46" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>46455</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>450000</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="47">
@@ -3025,33 +3080,35 @@
         <v>2</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I47" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>46783</v>
+      </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48">
@@ -3059,40 +3116,38 @@
         <v>13</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>46510</v>
+      </c>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="M48" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>46343</v>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>8960000</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="49">
@@ -3100,40 +3155,40 @@
         <v>13</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>46464</v>
+        <v>47052</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>11614285.7142857</v>
+        <v>550000</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50">
@@ -3141,102 +3196,102 @@
         <v>13</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>239</v>
+        <v>170</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>46398</v>
+        <v>46510</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2855555.55555556</v>
+        <v>450000</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>241</v>
+        <v>152</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>243</v>
+        <v>13</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>246</v>
+        <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3" t="n">
-        <v>275000000</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>46461</v>
+      </c>
+      <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>248</v>
+        <v>172</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>243</v>
+        <v>13</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>17</v>
@@ -3244,17 +3299,257 @@
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>46346</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="M53" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="L52" s="3" t="s">
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>225</v>
+      <c r="F54" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>46464</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>48596938</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>46398</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3" t="n">
+        <v>275000000</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>46486</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M52"/>
+  <autoFilter ref="A1:M58"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/outs/todo/top_results.xlsx
+++ b/outs/todo/top_results.xlsx
@@ -59,6 +59,27 @@
     <t xml:space="preserve">DHHS</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrated Viral Hepatitis Surveillance, Testing, Treatment, and Prevention Programs for Health Departments (IVH-STTP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCHHSTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forecasted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 139 days to deadline · about $7.5M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No escalation: required capabilities are in-house or contracted, no cost share, about 0.5 FTE fits your staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/2e580529-c869-47d0-9aab-7d0e239ed5e8</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-007</t>
   </si>
   <si>
@@ -68,9 +89,6 @@
     <t xml:space="preserve">HHS-HRSA</t>
   </si>
   <si>
-    <t xml:space="preserve">forecasted</t>
-  </si>
-  <si>
     <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $22.0M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
   </si>
   <si>
@@ -80,22 +98,16 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/c30fddfd-2094-4cf0-ba21-04b6736fc755</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrated Viral Hepatitis Surveillance, Testing, Treatment, and Prevention Programs for Health Departments (IVH-STTP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-CDC-NCHHSTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 139 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No escalation: required capabilities are in-house or contracted, no cost share, about 0.5 FTE fits your staff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/2e580529-c869-47d0-9aab-7d0e239ed5e8</t>
+    <t xml:space="preserve">HRSA-27-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) 2027 Service Area Competition (SAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $19.2M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/51fa7e21-beca-497f-a0f1-bf175382f77f</t>
   </si>
   <si>
     <t xml:space="preserve">CDC-RFA-CK-27-0007</t>
@@ -113,18 +125,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/38e79010-c2a9-4d5f-bf81-cede591318e4</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year (FY) 2027 Service Area Competition (SAC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 91 days to deadline · up to $19.2M (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/51fa7e21-beca-497f-a0f1-bf175382f77f</t>
-  </si>
-  <si>
     <t xml:space="preserve">HRSA-27-008</t>
   </si>
   <si>
@@ -146,6 +146,42 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/be465a8b-8694-4eef-9801-5160a92c7cdf</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controlling and Preventing STIs in US Health Departments (CAP-STIs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 103 days to deadline · about $8.5M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/0ff3ace3-70fb-4ef7-b6ba-b93a899a2707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strengthening Services to Prevent the Infectious Disease Consequences of Drug Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 236 days to deadline · about $41.2M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/441d2761-0d9c-42ae-a3da-905ce4ed0ca4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIV Care Grant Program - Part B States/Territories Formula and AIDS Drug Assistance Program Formula and AIDS Drug Assistance Program Supplemental Awards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 92 days to deadline · about $21.7M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/1d55627c-531e-4a60-95e0-719b256179bf</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-077</t>
   </si>
   <si>
@@ -170,6 +206,45 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/d9551b09-3a45-4dc1-a343-3f09521de9aa</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-DD-27-0065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surveillance and Case Control Study of Stillbirth and Birth Defects (SUCCSSBD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCBDDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 182 days to deadline · about $2.8M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/91d0d477-b844-4189-8880-bd7a2876b24e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holistic and Evidence-Informed Wellness for STI Prevention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 243 days to deadline · about $3.0M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/e511b41d-655a-4869-bfd3-09fbf0c33987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-DD-27-0028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maternal-Child Surveillance and Partnerships for Action, Results, and Knowledge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 208 days to deadline · about $2.2M per award (estimated: total ÷ expected awards) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/172926e9-5f18-4993-893d-ac73be5bbb9d</t>
+  </si>
+  <si>
     <t xml:space="preserve">RFA-IP-27-035</t>
   </si>
   <si>
@@ -185,6 +260,21 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/b3577f33-eee0-49fb-aeba-2ea0b02fe59e</t>
   </si>
   <si>
+    <t xml:space="preserve">FOR-FD-23-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufactured Foods Flexible Funding Model (MF-FFM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-FDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · no deadline stated · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
+  </si>
+  <si>
     <t xml:space="preserve">HRSA-27-019</t>
   </si>
   <si>
@@ -221,18 +311,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/741f2935-18c1-4e3e-8f54-f30dc3a6ee80</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controlling and Preventing STIs in US Health Departments (CAP-STIs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 103 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/0ff3ace3-70fb-4ef7-b6ba-b93a899a2707</t>
-  </si>
-  <si>
     <t xml:space="preserve">HRSA-27-046</t>
   </si>
   <si>
@@ -245,58 +323,16 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/6bc69d9c-87b7-4329-962c-16c8e3ad553d</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-DD-27-0065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surveillance and Case Control Study of Stillbirth and Birth Defects (SUCCSSBD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-CDC-NCBDDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 182 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/91d0d477-b844-4189-8880-bd7a2876b24e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DD-27-0028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maternal-Child Surveillance and Partnerships for Action, Results, and Knowledge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 208 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/172926e9-5f18-4993-893d-ac73be5bbb9d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holistic and Evidence-Informed Wellness for STI Prevention</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 243 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/e511b41d-655a-4869-bfd3-09fbf0c33987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOR-FD-23-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufactured Foods Flexible Funding Model (MF-FFM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-FDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · no deadline stated · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b8b51aae-68fc-448a-bbca-5fbfd229a841</t>
+    <t xml:space="preserve">HRSA-27-079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan White HIV/AIDS Program (RWHAP) Integrated HIV/AIDS Planning Resource Allocation Cooperative Agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 110 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
   </si>
   <si>
     <t xml:space="preserve">RFA-DP-27-051</t>
@@ -311,18 +347,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/54666d94-e0dc-44d3-90e6-6eb913f79ca9</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan White HIV/AIDS Program (RWHAP) Integrated HIV/AIDS Planning Resource Allocation Cooperative Agreement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 110 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/a73919b2-7a90-4735-8ec5-a67c08dea3ed</t>
-  </si>
-  <si>
     <t xml:space="preserve">RFA-OH-27-050</t>
   </si>
   <si>
@@ -359,18 +383,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/8bb15754-c013-462d-b305-f2a8dd116e08</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strengthening Services to Prevent the Infectious Disease Consequences of Drug Use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 236 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/441d2761-0d9c-42ae-a3da-905ce4ed0ca4</t>
-  </si>
-  <si>
     <t xml:space="preserve">HRSA-27-039</t>
   </si>
   <si>
@@ -395,18 +407,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/18c0a9f1-fe39-4c7a-8ffd-1d8c656d666f</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIV Care Grant Program - Part B States/Territories Formula and AIDS Drug Assistance Program Formula and AIDS Drug Assistance Program Supplemental Awards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 92 days to deadline · award not stated on Grants.gov · no cost share → Tier 1: writer can act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/1d55627c-531e-4a60-95e0-719b256179bf</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDC-RFA-TP22-2201</t>
   </si>
   <si>
@@ -428,67 +428,151 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/42a1b238-2c19-47b4-ae58-f4a775231b78</t>
   </si>
   <si>
+    <t xml:space="preserve">CDC-RFA-DP-27-0043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statewide Perinatal Quality Collaboratives: Improving Perinatal Care and Outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-CDC-NCCDPHP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 215 days to deadline · about $2.1M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/477f11ad-e8c7-40ea-84f3-f5bec6e50e3b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-2026-ACF-ORR-ZU-0019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Study and Post-Release Services for Unaccompanied Alien Children​​</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHS-ACF-ORR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 366 days to deadline · up to $100.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-CK-26-035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emerging Infections Network - Research for Preventing, Detecting, and Managing Travel-associated Infectious Diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · up to $6.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requires funding and monitoring subrecipients; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/10f4a697-e6a1-454a-bb73-74bc933f364a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-OH-24-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Center for Construction Safety and Health Research and Translation (U54)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · partner needed for research and rigorous evaluation · 62 days to deadline · up to $5.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b307f2ac-767d-4715-be92-f5326db2cd9d</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDC-RFA-DP-27-0072</t>
   </si>
   <si>
     <t xml:space="preserve">Promoting Population Health through Increased Capacity in Alcohol Epidemiology &amp; the Prevention of Excessive Alcohol Use</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-CDC-NCCDPHP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 212 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner</t>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 212 days to deadline · about $1.0M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/6d44bb23-2a1f-4e12-8d72-c2b5b46195d4</t>
   </si>
   <si>
-    <t xml:space="preserve">HHS-2026-ACF-ORR-ZU-0019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Study and Post-Release Services for Unaccompanied Alien Children​​</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHS-ACF-ORR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · partner needed for workforce training and credentialing · 366 days to deadline · up to $100.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/cb2cbb9f-741d-4e6b-ad32-557d751f9903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-CK-26-035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emerging Infections Network - Research for Preventing, Detecting, and Managing Travel-associated Infectious Diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · up to $6.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requires funding and monitoring subrecipients; Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/10f4a697-e6a1-454a-bb73-74bc933f364a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-OH-24-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Center for Construction Safety and Health Research and Translation (U54)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · partner needed for research and rigorous evaluation · 62 days to deadline · up to $5.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b307f2ac-767d-4715-be92-f5326db2cd9d</t>
+    <t xml:space="preserve">HRSA-27-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year (FY) 2027 State and Regional Primary Care Association (PCA) Cooperative Agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing; partner needed for emergency management · 117 days to deadline · up to $4.9M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Needs emergency management, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFA-DP-27-036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot Testing, Implementation, and Evaluation of the Cervical, Breast and Colorectal Cancer Clinical Decision Support Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 174 days to deadline · about $3.6M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/5686905a-446f-4b0d-8885-e1683d35c3f4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rural Communities Opioid Response Program - Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 174 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infant-Toddler Court Program–National Resource Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $6.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/910a75ad-0418-4091-a436-703280874498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Home Visiting Research, Improvement, Sustainability and Evaluation Center (HV-RISE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 146 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
   </si>
   <si>
     <t xml:space="preserve">HRSA-27-042</t>
@@ -506,21 +590,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/02b2d236-f596-4aca-874d-b8e364156ddc</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year (FY) 2027 State and Regional Primary Care Association (PCA) Cooperative Agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing; partner needed for emergency management · 117 days to deadline · up to $4.9M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner; Needs emergency management, which DHHS reaches only through a partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/88f12b64-0fbc-44ea-a689-57ed9e9fb9dd</t>
-  </si>
-  <si>
     <t xml:space="preserve">CDC-RFA-CE-27-0024</t>
   </si>
   <si>
@@ -539,46 +608,28 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/3c36bc50-73ae-42ad-a727-fae640dad5c9</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infant-Toddler Court Program–National Resource Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $6.8M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs workforce training and credentialing, which DHHS reaches only through a partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/910a75ad-0418-4091-a436-703280874498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rural Communities Opioid Response Program - Evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 174 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs research and rigorous evaluation, which DHHS reaches only through a partner; Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/44a089ce-dd0a-4cde-b6f4-c77d08d56a08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRSA-27-023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Home Visiting Research, Improvement, Sustainability and Evaluation Center (HV-RISE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 146 days to deadline · up to $5.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/b9bdeaa2-068f-4aa9-960a-948c0b0a9bfd</t>
+    <t xml:space="preserve">CDC-RFA-PS-27-0011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Viral Hepatitis Education, Awareness, and Capacity Building for Communities and Providers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 244 days to deadline · about $2.8M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRSA-27-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infant-Toddler Court Program–State Awards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/3fe27753-0c94-4aa0-b7fb-09712631f269</t>
   </si>
   <si>
     <t xml:space="preserve">RFA-OH-27-049</t>
@@ -593,16 +644,46 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/43e32c6d-fbbd-4056-8fd4-f64cdebefd41</t>
   </si>
   <si>
-    <t xml:space="preserve">HRSA-27-021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infant-Toddler Court Program–State Awards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 203 days to deadline · up to $700K (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/3fe27753-0c94-4aa0-b7fb-09712631f269</t>
+    <t xml:space="preserve">CDC-RFA-CE-27-0039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core State Injury Prevention Program (Core SIPP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 159 days to deadline · about $1.4M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC-RFA-PS-27-0061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonstration Projects for Whole-Person Health Models for Women Living with HIV in the South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 166 days to deadline · about $2.5M per award (estimated: total ÷ expected awards) · no cost share → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/06024144-a58a-42d8-8813-75357d9bb7fe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHS-26-MT-144-000-99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal Year 2026 Flood Mitigation Assistance Swift Current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHS-DHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 488 days to deadline · award not stated on Grants.gov · cost share required (25% stated) → Tier 2: needs supervisor or division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost share required (25% stated): supervisor must approve match</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simpler.grants.gov/opportunity/4802584e-01a8-4435-9ce9-710fbc85cba0</t>
   </si>
   <si>
     <t xml:space="preserve">RFA-CK-26-036</t>
@@ -614,9 +695,6 @@
     <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 36 days to deadline · up to $1.0M (Grants.gov ceiling) · no cost share → Tier 2: needs supervisor or division</t>
   </si>
   <si>
-    <t xml:space="preserve">Cooperative agreement with a required evaluation</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/1a3231f6-36eb-40d1-afe8-232010fa2fe3</t>
   </si>
   <si>
@@ -632,72 +710,6 @@
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/9accc70c-9683-4b78-bb7b-e8fdbcff1b47</t>
   </si>
   <si>
-    <t xml:space="preserve">CDC-RFA-CE-27-0039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core State Injury Prevention Program (Core SIPP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 159 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/23b80a6d-ae96-4b02-b4ae-69093f8939d5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFA-DP-27-036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilot Testing, Implementation, and Evaluation of the Cervical, Breast and Colorectal Cancer Clinical Decision Support Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · required capabilities in-house or contracted · 174 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/5686905a-446f-4b0d-8885-e1683d35c3f4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Viral Hepatitis Education, Awareness, and Capacity Building for Communities and Providers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for workforce training and credentialing · 244 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/f931e3f2-28c6-4bcb-83ff-894bc6b2266c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHS-26-MT-144-000-99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal Year 2026 Flood Mitigation Assistance Swift Current</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHS-DHS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply · required capabilities in-house or contracted · 488 days to deadline · award not stated on Grants.gov · cost share required (25% stated) → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost share required (25% stated): supervisor must approve match</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/4802584e-01a8-4435-9ce9-710fbc85cba0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-DP-27-0043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statewide Perinatal Quality Collaboratives: Improving Perinatal Care and Outcomes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 215 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/477f11ad-e8c7-40ea-84f3-f5bec6e50e3b</t>
-  </si>
-  <si>
     <t xml:space="preserve">RFA-OH-25-003</t>
   </si>
   <si>
@@ -720,18 +732,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://simpler.grants.gov/opportunity/f2ea8925-6244-47e8-8de5-ffe0007096e7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC-RFA-PS-27-0061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demonstration Projects for Whole-Person Health Models for Women Living with HIV in the South</t>
-  </si>
-  <si>
-    <t xml:space="preserve">state agency can apply, forecast (not yet posted) · partner needed for research and rigorous evaluation · 166 days to deadline · award not stated on Grants.gov · no cost share → Tier 2: needs supervisor or division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://simpler.grants.gov/opportunity/06024144-a58a-42d8-8813-75357d9bb7fe</t>
   </si>
   <si>
     <t xml:space="preserve">VA-GPD-FORECAST-FY2026-FY2028</t>
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>14</v>
@@ -1279,10 +1279,10 @@
         <v>17</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>46386</v>
+        <v>46434</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>22024900</v>
+        <v>7500000</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>18</v>
@@ -1320,9 +1320,11 @@
         <v>17</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>46434</v>
-      </c>
-      <c r="J3" s="3"/>
+        <v>46386</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>22024900</v>
+      </c>
       <c r="K3" s="3" t="s">
         <v>24</v>
       </c>
@@ -1353,25 +1355,25 @@
         <v>28</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>46386</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>19182000</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>46391</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>22000000</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -1385,25 +1387,25 @@
         <v>4</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>46386</v>
+        <v>46391</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>19182000</v>
+        <v>22000000</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>34</v>
@@ -1432,10 +1434,10 @@
         <v>36</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>17</v>
@@ -1450,7 +1452,7 @@
         <v>37</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>38</v>
@@ -1467,7 +1469,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>39</v>
@@ -1476,7 +1478,7 @@
         <v>40</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>17</v>
@@ -1491,7 +1493,7 @@
         <v>41</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>42</v>
@@ -1508,7 +1510,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>43</v>
@@ -1523,10 +1525,10 @@
         <v>17</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>46328</v>
+        <v>46398</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>10000000</v>
+        <v>8474576.27118644</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>45</v>
@@ -1549,7 +1551,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>47</v>
@@ -1564,16 +1566,16 @@
         <v>17</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>46407</v>
+        <v>46531</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>5149000</v>
+        <v>41250000</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>49</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>50</v>
@@ -1590,7 +1592,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>51</v>
@@ -1599,7 +1601,7 @@
         <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>17</v>
@@ -1608,16 +1610,16 @@
         <v>46387</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1140000</v>
+        <v>21716666.6666667</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -1631,34 +1633,34 @@
         <v>10</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>46328</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>46357</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -1672,13 +1674,13 @@
         <v>11</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
@@ -1687,19 +1689,19 @@
         <v>17</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>46438</v>
+        <v>46407</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1000000</v>
+        <v>5149000</v>
       </c>
       <c r="K12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -1713,31 +1715,31 @@
         <v>12</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>46497</v>
+        <v>46477</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1000000</v>
+        <v>2750000</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>66</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>67</v>
@@ -1754,7 +1756,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>68</v>
@@ -1763,20 +1765,22 @@
         <v>69</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>46398</v>
-      </c>
-      <c r="J14" s="3"/>
+        <v>46538</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>3000000</v>
+      </c>
       <c r="K14" s="3" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>71</v>
@@ -1793,7 +1797,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>72</v>
@@ -1802,16 +1806,16 @@
         <v>73</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>46464</v>
+        <v>46503</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>750000</v>
+        <v>2217391.30434783</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>74</v>
@@ -1834,7 +1838,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>76</v>
@@ -1849,14 +1853,16 @@
         <v>17</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>46477</v>
-      </c>
-      <c r="J16" s="3"/>
+        <v>46387</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>1140000</v>
+      </c>
       <c r="K16" s="3" t="s">
         <v>79</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>80</v>
@@ -1882,23 +1888,21 @@
         <v>82</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>46503</v>
-      </c>
+      <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
@@ -1912,13 +1916,13 @@
         <v>17</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
@@ -1927,17 +1931,19 @@
         <v>17</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>46538</v>
-      </c>
-      <c r="J18" s="3"/>
+        <v>46357</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>1000000</v>
+      </c>
       <c r="K18" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
@@ -1951,27 +1957,31 @@
         <v>18</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+      <c r="I19" s="3" t="n">
+        <v>46438</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>1000000</v>
+      </c>
       <c r="K19" s="3" t="s">
         <v>92</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>93</v>
@@ -1988,7 +1998,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>94</v>
@@ -1997,22 +2007,22 @@
         <v>95</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>46468</v>
+        <v>46497</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>725000</v>
+        <v>1000000</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>96</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>97</v>
@@ -2029,7 +2039,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>98</v>
@@ -2038,16 +2048,16 @@
         <v>99</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>46405</v>
+        <v>46464</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>700000</v>
+        <v>750000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>100</v>
@@ -2070,7 +2080,7 @@
         <v>21</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>102</v>
@@ -2079,22 +2089,22 @@
         <v>103</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>46386</v>
+        <v>46405</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>685000</v>
+        <v>700000</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>104</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>105</v>
@@ -2111,7 +2121,7 @@
         <v>22</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>106</v>
@@ -2120,22 +2130,22 @@
         <v>107</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>46466</v>
+        <v>46468</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>650000</v>
+        <v>725000</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>108</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>109</v>
@@ -2152,7 +2162,7 @@
         <v>23</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>110</v>
@@ -2161,16 +2171,16 @@
         <v>111</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>46462</v>
+        <v>46386</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>500000</v>
+        <v>685000</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>112</v>
@@ -2208,14 +2218,16 @@
         <v>17</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>46531</v>
-      </c>
-      <c r="J25" s="3"/>
+        <v>46466</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>650000</v>
+      </c>
       <c r="K25" s="3" t="s">
         <v>116</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>117</v>
@@ -2232,7 +2244,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>118</v>
@@ -2241,13 +2253,13 @@
         <v>119</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>46532</v>
+        <v>46462</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>500000</v>
@@ -2256,7 +2268,7 @@
         <v>120</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>121</v>
@@ -2273,7 +2285,7 @@
         <v>26</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>122</v>
@@ -2282,22 +2294,22 @@
         <v>123</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>46508</v>
+        <v>46532</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>124</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>125</v>
@@ -2314,7 +2326,7 @@
         <v>27</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>126</v>
@@ -2323,20 +2335,22 @@
         <v>127</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>46387</v>
-      </c>
-      <c r="J28" s="3"/>
+        <v>46508</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>300000</v>
+      </c>
       <c r="K28" s="3" t="s">
         <v>128</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>129</v>
@@ -2394,7 +2408,7 @@
         <v>2</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>137</v>
@@ -2409,9 +2423,11 @@
         <v>17</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>46507</v>
-      </c>
-      <c r="J30" s="3"/>
+        <v>46510</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>2141025.64102564</v>
+      </c>
       <c r="K30" s="3" t="s">
         <v>140</v>
       </c>
@@ -2483,7 +2499,7 @@
         <v>150</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>133</v>
@@ -2524,7 +2540,7 @@
         <v>155</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>133</v>
@@ -2565,25 +2581,25 @@
         <v>159</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>46483</v>
+        <v>46507</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>500000</v>
+        <v>1002916.66666667</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>160</v>
       </c>
       <c r="L34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="M34" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="35">
@@ -2600,13 +2616,13 @@
         <v>58</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="G35" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>17</v>
@@ -2618,13 +2634,13 @@
         <v>4900000</v>
       </c>
       <c r="K35" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="L35" s="3" t="s">
+      <c r="M35" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="36">
@@ -2641,31 +2657,31 @@
         <v>58</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>46469</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>3625000</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="L36" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>46494</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="K36" s="3" t="s">
+      <c r="M36" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="37">
@@ -2679,34 +2695,34 @@
         <v>9</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>46469</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="L37" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>46498</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>6750000</v>
-      </c>
-      <c r="K37" s="3" t="s">
+      <c r="M37" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="38">
@@ -2723,31 +2739,31 @@
         <v>57</v>
       </c>
       <c r="E38" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>46498</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="L38" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>46469</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="K38" s="3" t="s">
+      <c r="M38" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="39">
@@ -2764,13 +2780,13 @@
         <v>56</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>17</v>
@@ -2782,13 +2798,13 @@
         <v>5000000</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>141</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40">
@@ -2802,34 +2818,34 @@
         <v>12</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>46483</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="L40" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>46444</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="K40" s="3" t="s">
+      <c r="M40" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="41">
@@ -2843,34 +2859,34 @@
         <v>13</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E41" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>46498</v>
+        <v>46494</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>700000</v>
+        <v>1200000</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>194</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42">
@@ -2884,31 +2900,31 @@
         <v>14</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>46331</v>
+        <v>46539</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>1000000</v>
+        <v>2750000</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>200</v>
@@ -2925,7 +2941,7 @@
         <v>15</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>201</v>
@@ -2934,22 +2950,22 @@
         <v>202</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>46455</v>
+        <v>46498</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>900000</v>
+        <v>700000</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>203</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>204</v>
@@ -2966,7 +2982,7 @@
         <v>16</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>205</v>
@@ -2975,20 +2991,22 @@
         <v>206</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>46454</v>
-      </c>
-      <c r="J44" s="3"/>
+        <v>46444</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>1400000</v>
+      </c>
       <c r="K44" s="3" t="s">
         <v>207</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>208</v>
@@ -3005,7 +3023,7 @@
         <v>17</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>209</v>
@@ -3014,20 +3032,22 @@
         <v>210</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>53</v>
+        <v>193</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>46469</v>
-      </c>
-      <c r="J45" s="3"/>
+        <v>46454</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>1423076.92307692</v>
+      </c>
       <c r="K45" s="3" t="s">
         <v>211</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>212</v>
@@ -3044,7 +3064,7 @@
         <v>18</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>213</v>
@@ -3053,20 +3073,22 @@
         <v>214</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>46539</v>
-      </c>
-      <c r="J46" s="3"/>
+        <v>46461</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>2500000</v>
+      </c>
       <c r="K46" s="3" t="s">
         <v>215</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>216</v>
@@ -3122,7 +3144,7 @@
         <v>20</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>223</v>
@@ -3131,20 +3153,22 @@
         <v>224</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>46510</v>
-      </c>
-      <c r="J48" s="3"/>
+        <v>46331</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>1000000</v>
+      </c>
       <c r="K48" s="3" t="s">
         <v>225</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>226</v>
@@ -3161,7 +3185,7 @@
         <v>21</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>227</v>
@@ -3170,22 +3194,22 @@
         <v>228</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>47052</v>
+        <v>46455</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>550000</v>
+        <v>900000</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>229</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>230</v>
@@ -3202,7 +3226,7 @@
         <v>22</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>231</v>
@@ -3211,22 +3235,22 @@
         <v>232</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>170</v>
+        <v>78</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>46510</v>
+        <v>47052</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>450000</v>
+        <v>550000</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>233</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>234</v>
@@ -3243,7 +3267,7 @@
         <v>23</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>235</v>
@@ -3252,20 +3276,22 @@
         <v>236</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>46461</v>
-      </c>
-      <c r="J51" s="3"/>
+        <v>46510</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>450000</v>
+      </c>
       <c r="K51" s="3" t="s">
         <v>237</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>238</v>
@@ -3369,7 +3395,7 @@
         <v>252</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>17</v>
